--- a/sheets/대금율보/검수/김매기노래.xlsx
+++ b/sheets/대금율보/검수/김매기노래.xlsx
@@ -5659,8 +5659,7 @@
         <is>
           <t xml:space="preserve">潢
 汰
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="S6" s="26" t="inlineStr">
@@ -6026,8 +6025,7 @@
       </c>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="M10" s="26" t="inlineStr">
@@ -6333,8 +6331,7 @@
         <is>
           <t xml:space="preserve">–
 汰
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="E14" s="26" t="inlineStr">
@@ -6398,8 +6395,7 @@
       <c r="Q14" s="26"/>
       <c r="R14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="S14" s="26" t="inlineStr">

--- a/sheets/대금율보/검수/김매기노래.xlsx
+++ b/sheets/대금율보/검수/김매기노래.xlsx
@@ -5259,32 +5259,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="81.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="91.25" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
       <c r="T3" s="21"/>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="91.25" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
       <c r="T4" s="21"/>
       <c r="U4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="91.25" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="91.25" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="U6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="91.25" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22"/>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="91.25" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="25"/>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="91.25" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="25"/>
@@ -5967,7 +5967,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="91.25" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
       <c r="T10" s="21"/>
       <c r="U10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="91.25" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -6147,7 +6147,7 @@
       <c r="T11" s="21"/>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="91.25" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="25"/>
@@ -6232,7 +6232,7 @@
       <c r="T12" s="21"/>
       <c r="U12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="91.25" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
@@ -6323,7 +6323,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="91.25" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="26"/>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="U14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="91.25" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="91.25" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="25"/>
@@ -6572,7 +6572,7 @@
       <c r="T16" s="21"/>
       <c r="U16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="91.25" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="25"/>
@@ -6661,7 +6661,7 @@
       <c r="T17" s="21"/>
       <c r="U17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="91.25" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="26"/>
@@ -6734,6 +6734,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
 </worksheet>
 </file>